--- a/bizconfig/static-xlsx/moba/pixel_moba/map_arena.xlsx
+++ b/bizconfig/static-xlsx/moba/pixel_moba/map_arena.xlsx
@@ -4,32 +4,52 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" tabRatio="600" autoFilterDateGrouping="true"/>
   </bookViews>
   <sheets>
-    <sheet name="MapArena" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="MapBase" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="MapLane" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="MapRiver" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="MapTower" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="MapWall" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="MapBush" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="MapMonsterSpawn" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="MapArena" sheetId="1" r:id="rId1" state="visible"/>
+    <sheet name="MapBase" sheetId="2" r:id="rId2" state="visible"/>
+    <sheet name="MapLane" sheetId="3" r:id="rId3" state="visible"/>
+    <sheet name="MapRiver" sheetId="4" r:id="rId4" state="visible"/>
+    <sheet name="MapTower" sheetId="5" r:id="rId5" state="visible"/>
+    <sheet name="MapWall" sheetId="6" r:id="rId6" state="visible"/>
+    <sheet name="MapBush" sheetId="7" r:id="rId7" state="visible"/>
+    <sheet name="MapMonsterSpawn" sheetId="8" r:id="rId8" state="visible"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="124519" fullCalcOnLoad="true"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+  <si>
+    <t>unit_id</t>
+  </si>
+  <si>
+    <t>uint32</t>
+  </si>
+  <si>
+    <t>notnull</t>
+  </si>
+  <si>
+    <t>!s!c</t>
+  </si>
+  <si>
+    <t>外键 -&gt; unit.id</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -54,12 +74,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="false"/>
   </cellStyles>
-  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -132,7 +152,7 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Office Theme">
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
@@ -1767,9 +1787,9 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
   <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <outlinePr summaryBelow="true" summaryRight="true"/>
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:D14"/>
@@ -1796,6 +1816,9 @@
           <t>rect</t>
         </is>
       </c>
+      <c r="E1" t="s">
+        <v>0</v>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1818,6 +1841,9 @@
           <t>string</t>
         </is>
       </c>
+      <c r="E2" t="s">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1840,6 +1866,9 @@
           <t>notnull</t>
         </is>
       </c>
+      <c r="E3" t="s">
+        <v>2</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1862,6 +1891,9 @@
           <t>!s!c</t>
         </is>
       </c>
+      <c r="E4" t="s">
+        <v>3</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1884,6 +1916,9 @@
           <t>[x,y,w,h] JSON</t>
         </is>
       </c>
+      <c r="E5" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1904,6 +1939,9 @@
           <t>[22,30,3,3]</t>
         </is>
       </c>
+      <c r="E6">
+        <v>4001</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1924,6 +1962,9 @@
           <t>[16,54,2,2]</t>
         </is>
       </c>
+      <c r="E7">
+        <v>4002</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1944,6 +1985,9 @@
           <t>[34,58,2,2]</t>
         </is>
       </c>
+      <c r="E8">
+        <v>4003</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1964,6 +2008,9 @@
           <t>[24,18,2,2]</t>
         </is>
       </c>
+      <c r="E9">
+        <v>4004</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1984,6 +2031,9 @@
           <t>[125,117,3,3]</t>
         </is>
       </c>
+      <c r="E10">
+        <v>4001</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -2004,6 +2054,9 @@
           <t>[132,94,2,2]</t>
         </is>
       </c>
+      <c r="E11">
+        <v>4002</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2024,6 +2077,9 @@
           <t>[114,90,2,2]</t>
         </is>
       </c>
+      <c r="E12">
+        <v>4003</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2044,6 +2100,9 @@
           <t>[124,130,2,2]</t>
         </is>
       </c>
+      <c r="E13">
+        <v>4004</v>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2063,6 +2122,9 @@
         <is>
           <t>[73,72,4,4]</t>
         </is>
+      </c>
+      <c r="E14">
+        <v>4005</v>
       </c>
     </row>
   </sheetData>

--- a/bizconfig/static-xlsx/moba/pixel_moba/map_arena.xlsx
+++ b/bizconfig/static-xlsx/moba/pixel_moba/map_arena.xlsx
@@ -4,52 +4,32 @@
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" tabRatio="600" autoFilterDateGrouping="true"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="MapArena" sheetId="1" r:id="rId1" state="visible"/>
-    <sheet name="MapBase" sheetId="2" r:id="rId2" state="visible"/>
-    <sheet name="MapLane" sheetId="3" r:id="rId3" state="visible"/>
-    <sheet name="MapRiver" sheetId="4" r:id="rId4" state="visible"/>
-    <sheet name="MapTower" sheetId="5" r:id="rId5" state="visible"/>
-    <sheet name="MapWall" sheetId="6" r:id="rId6" state="visible"/>
-    <sheet name="MapBush" sheetId="7" r:id="rId7" state="visible"/>
-    <sheet name="MapMonsterSpawn" sheetId="8" r:id="rId8" state="visible"/>
+    <sheet name="MapArena" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="MapBase" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="MapLane" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="MapRiver" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="MapTower" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="MapWall" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="MapBush" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="MapMonsterSpawn" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="true"/>
+  <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
-  <si>
-    <t>unit_id</t>
-  </si>
-  <si>
-    <t>uint32</t>
-  </si>
-  <si>
-    <t>notnull</t>
-  </si>
-  <si>
-    <t>!s!c</t>
-  </si>
-  <si>
-    <t>外键 -&gt; unit.id</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:ap="http://schemas.openxmlformats.org/officeDocument/2006/extended-properties" xmlns:op="http://schemas.openxmlformats.org/officeDocument/2006/custom-properties" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:cdr="http://schemas.openxmlformats.org/drawingml/2006/chartDrawing" xmlns:comp="http://schemas.openxmlformats.org/drawingml/2006/compatibility" xmlns:dgm="http://schemas.openxmlformats.org/drawingml/2006/diagram" xmlns:lc="http://schemas.openxmlformats.org/drawingml/2006/lockedCanvas" xmlns:pic="http://schemas.openxmlformats.org/drawingml/2006/picture" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" xmlns:m="http://schemas.openxmlformats.org/officeDocument/2006/math" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:sl="http://schemas.openxmlformats.org/schemaLibrary/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xne="http://schemas.microsoft.com/office/excel/2006/main" xmlns:mso="http://schemas.microsoft.com/office/2006/01/customui" xmlns:ax="http://schemas.microsoft.com/office/2006/activeX" xmlns:cppr="http://schemas.microsoft.com/office/2006/coverPageProps" xmlns:cdip="http://schemas.microsoft.com/office/2006/customDocumentInformationPanel" xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ntns="http://schemas.microsoft.com/office/2006/metadata/customXsn" xmlns:lp="http://schemas.microsoft.com/office/2006/metadata/longProperties" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" xmlns:msink="http://schemas.microsoft.com/ink/2010/main" xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" xmlns:cdr14="http://schemas.microsoft.com/office/drawing/2010/chartDrawing" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" xmlns:pic14="http://schemas.microsoft.com/office/drawing/2010/picture" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xdr14="http://schemas.microsoft.com/office/excel/2010/spreadsheetDrawing" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:dsp="http://schemas.microsoft.com/office/drawing/2008/diagram" xmlns:mso14="http://schemas.microsoft.com/office/2009/07/customui" xmlns:dgm14="http://schemas.microsoft.com/office/drawing/2010/diagram" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:x12ac="http://schemas.microsoft.com/office/spreadsheetml/2011/1/ac" xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" xmlns:xr4="http://schemas.microsoft.com/office/spreadsheetml/2016/revision4" xmlns:xr5="http://schemas.microsoft.com/office/spreadsheetml/2016/revision5" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr7="http://schemas.microsoft.com/office/spreadsheetml/2016/revision7" xmlns:xr8="http://schemas.microsoft.com/office/spreadsheetml/2016/revision8" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr11="http://schemas.microsoft.com/office/spreadsheetml/2016/revision11" xmlns:xr12="http://schemas.microsoft.com/office/spreadsheetml/2016/revision12" xmlns:xr13="http://schemas.microsoft.com/office/spreadsheetml/2016/revision13" xmlns:xr14="http://schemas.microsoft.com/office/spreadsheetml/2016/revision14" xmlns:xr15="http://schemas.microsoft.com/office/spreadsheetml/2016/revision15" xmlns:x16="http://schemas.microsoft.com/office/spreadsheetml/2014/11/main" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:mo="http://schemas.microsoft.com/office/mac/office/2008/main" xmlns:mx="http://schemas.microsoft.com/office/mac/excel/2008/main" xmlns:mv="urn:schemas-microsoft-com:mac:vml" xmlns:o="urn:schemas-microsoft-com:office:office" xmlns:v="urn:schemas-microsoft-com:vml" mc:Ignorable="c14 cdr14 a14 pic14 x14 xdr14 x14ac dsp mso14 dgm14 x15 x12ac x15ac xr xr2 xr3 xr4 xr5 xr6 xr7 xr8 xr9 xr10 xr11 xr12 xr13 xr14 xr15 x15 x16 x16r2 mo mx mv o v" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
   <fonts count="1">
     <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <color theme="1"/>
+      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -74,12 +54,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="false" pivotButton="false"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="false"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <tableStyles count="0" defaultPivotStyle="PivotStyleLight16" defaultTableStyle="TableStyleMedium9"/>
+  <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -1120,7 +1100,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:G9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1144,6 +1124,21 @@
           <t>rect</t>
         </is>
       </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>unit_id</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>lane</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>tier</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1166,6 +1161,21 @@
           <t>string</t>
         </is>
       </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1188,6 +1198,21 @@
           <t>notnull</t>
         </is>
       </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>notnull</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>notnull</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>notnull</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1210,6 +1235,21 @@
           <t>!s!c</t>
         </is>
       </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>!s!c</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>!s!c</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>!s!c</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1232,6 +1272,21 @@
           <t>[x,y,w,h] JSON</t>
         </is>
       </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>外键 -&gt; unit.id</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0 top/1 mid/2 bot</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>0 外塔/1 内塔/2 水晶</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1252,6 +1307,15 @@
           <t>[41,40,4,4]</t>
         </is>
       </c>
+      <c r="E6" t="n">
+        <v>3001</v>
+      </c>
+      <c r="F6" t="n">
+        <v>0</v>
+      </c>
+      <c r="G6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1272,6 +1336,15 @@
           <t>[105,40,4,4]</t>
         </is>
       </c>
+      <c r="E7" t="n">
+        <v>3002</v>
+      </c>
+      <c r="F7" t="n">
+        <v>2</v>
+      </c>
+      <c r="G7" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1292,6 +1365,15 @@
           <t>[41,106,4,4]</t>
         </is>
       </c>
+      <c r="E8" t="n">
+        <v>3101</v>
+      </c>
+      <c r="F8" t="n">
+        <v>0</v>
+      </c>
+      <c r="G8" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1311,6 +1393,15 @@
         <is>
           <t>[105,106,4,4]</t>
         </is>
+      </c>
+      <c r="E9" t="n">
+        <v>3102</v>
+      </c>
+      <c r="F9" t="n">
+        <v>2</v>
+      </c>
+      <c r="G9" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1787,12 +1878,12 @@
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
-    <outlinePr summaryBelow="true" summaryRight="true"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D14"/>
+  <dimension ref="A1:E14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1816,8 +1907,10 @@
           <t>rect</t>
         </is>
       </c>
-      <c r="E1" t="s">
-        <v>0</v>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>unit_id</t>
+        </is>
       </c>
     </row>
     <row r="2">
@@ -1841,8 +1934,10 @@
           <t>string</t>
         </is>
       </c>
-      <c r="E2" t="s">
-        <v>1</v>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>uint32</t>
+        </is>
       </c>
     </row>
     <row r="3">
@@ -1866,8 +1961,10 @@
           <t>notnull</t>
         </is>
       </c>
-      <c r="E3" t="s">
-        <v>2</v>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>notnull</t>
+        </is>
       </c>
     </row>
     <row r="4">
@@ -1891,8 +1988,10 @@
           <t>!s!c</t>
         </is>
       </c>
-      <c r="E4" t="s">
-        <v>3</v>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>!s!c</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -1916,8 +2015,10 @@
           <t>[x,y,w,h] JSON</t>
         </is>
       </c>
-      <c r="E5" t="s">
-        <v>4</v>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>外键 -&gt; unit.id</t>
+        </is>
       </c>
     </row>
     <row r="6">
@@ -1939,7 +2040,7 @@
           <t>[22,30,3,3]</t>
         </is>
       </c>
-      <c r="E6">
+      <c r="E6" t="n">
         <v>4001</v>
       </c>
     </row>
@@ -1962,7 +2063,7 @@
           <t>[16,54,2,2]</t>
         </is>
       </c>
-      <c r="E7">
+      <c r="E7" t="n">
         <v>4002</v>
       </c>
     </row>
@@ -1985,7 +2086,7 @@
           <t>[34,58,2,2]</t>
         </is>
       </c>
-      <c r="E8">
+      <c r="E8" t="n">
         <v>4003</v>
       </c>
     </row>
@@ -2008,7 +2109,7 @@
           <t>[24,18,2,2]</t>
         </is>
       </c>
-      <c r="E9">
+      <c r="E9" t="n">
         <v>4004</v>
       </c>
     </row>
@@ -2031,7 +2132,7 @@
           <t>[125,117,3,3]</t>
         </is>
       </c>
-      <c r="E10">
+      <c r="E10" t="n">
         <v>4001</v>
       </c>
     </row>
@@ -2054,7 +2155,7 @@
           <t>[132,94,2,2]</t>
         </is>
       </c>
-      <c r="E11">
+      <c r="E11" t="n">
         <v>4002</v>
       </c>
     </row>
@@ -2077,7 +2178,7 @@
           <t>[114,90,2,2]</t>
         </is>
       </c>
-      <c r="E12">
+      <c r="E12" t="n">
         <v>4003</v>
       </c>
     </row>
@@ -2100,7 +2201,7 @@
           <t>[124,130,2,2]</t>
         </is>
       </c>
-      <c r="E13">
+      <c r="E13" t="n">
         <v>4004</v>
       </c>
     </row>
@@ -2123,7 +2224,7 @@
           <t>[73,72,4,4]</t>
         </is>
       </c>
-      <c r="E14">
+      <c r="E14" t="n">
         <v>4005</v>
       </c>
     </row>
